--- a/output/pdf_financials_xlsx/NP.xlsx
+++ b/output/pdf_financials_xlsx/NP.xlsx
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>20.601699</v>
+        <v>23.437967</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>22.955348</v>
+        <v>31.082472</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>20.601699</v>
+        <v>24.005106</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -5338,7 +5338,11 @@
           <t>Warrant reserve (note 16 (c)) 2,876,463</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -8703,7 +8707,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NP.xlsx
+++ b/output/pdf_financials_xlsx/NP.xlsx
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.368223</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.369227</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.200824</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.368223</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.369227</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.200824</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.54611</v>
+        <v>3.177887</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.290418</v>
+        <v>2.921191</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.598496</v>
+        <v>2.397672</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/NP.xlsx
+++ b/output/pdf_financials_xlsx/NP.xlsx
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.97784</v>
+        <v>2.632339</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>3.112088</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.212441</v>
+        <v>0.699686</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.212441</v>
+        <v>2.937662</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.204219</v>
+        <v>1.550282</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.931568</v>
+        <v>-10.444323</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-27.983367</v>
+        <v>-25.258146</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-13.795489</v>
+        <v>-12.449426</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1634.570773640682</v>
+        <v>-1561.714213941053</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1782.148497902183</v>
+        <v>-1608.590094025999</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-748.7054286410514</v>
+        <v>-675.6522244093741</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.075886</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.199472</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0.511475</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.284123</v>
+        <v>0.360009</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.660228</v>
+        <v>0.8597</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.721759</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.177887</v>
+        <v>3.102001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.921191</v>
+        <v>2.721719</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.397672</v>
@@ -13408,7 +13408,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -14644,7 +14648,11 @@
           <t>Amortization expense D 1,383,371</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -15848,7 +15856,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -16137,7 +16149,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
